--- a/docs/【キャラ_002】ときめきポケット_03稿.xlsx
+++ b/docs/【キャラ_002】ときめきポケット_03稿.xlsx
@@ -586,7 +586,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>・BGMは曲が決まっていないため「仮BGM_曲調名」で指定しています。曲が決まったら素材シートで差し替えます</t>
+          <t>・BGMは選曲済みです。宴（test260903.xlsx の Sound シート）の登録名「BGM_○○」で指定しています（曲名とファイル名は素材シートを参照）</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       <c r="F3" s="7" t="inlineStr">
         <is>
           <t>背景：黒
-BGM：仮BGM_不穏</t>
+BGM：BGM_不穏</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -2803,7 +2803,7 @@
       <c r="F39" s="7" t="inlineStr">
         <is>
           <t>背景：空港
-BGM：仮BGM_日常コミカル
+BGM：BGM_日常コミカル
 美鈴の表情：喜び</t>
         </is>
       </c>
@@ -4633,7 +4633,7 @@
       <c r="E109" s="6" t="n"/>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_緊迫
+          <t>BGM：BGM_緊迫
 美鈴の表情：怒り</t>
         </is>
       </c>
@@ -4979,7 +4979,7 @@
       <c r="E122" s="6" t="n"/>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_バトル</t>
+          <t>BGM：BGM_バトル</t>
         </is>
       </c>
       <c r="G122" s="6" t="n"/>
@@ -5184,7 +5184,7 @@
       <c r="F3" s="7" t="inlineStr">
         <is>
           <t>背景：黒
-BGM：仮BGM_バトル</t>
+BGM：BGM_バトル</t>
         </is>
       </c>
       <c r="G3" s="6" t="n"/>
@@ -5304,7 +5304,7 @@
       <c r="F8" s="7" t="inlineStr">
         <is>
           <t>背景：街中
-BGM：仮BGM_日常コミカル
+BGM：BGM_日常コミカル
 美鈴の表情：通常</t>
         </is>
       </c>
@@ -6060,7 +6060,7 @@
       <c r="F37" s="7" t="inlineStr">
         <is>
           <t>背景：車内（ハマー）
-BGM：仮BGM_緊迫</t>
+BGM：BGM_緊迫</t>
         </is>
       </c>
       <c r="G37" s="6" t="n"/>
@@ -6689,7 +6689,7 @@
       <c r="E62" s="6" t="n"/>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_日常コミカル
+          <t>BGM：BGM_日常コミカル
 美鈴の表情：喜び</t>
         </is>
       </c>
@@ -7277,7 +7277,7 @@
 SE：車の衝突
 SE：ガラスが割れる
 画面揺れ（大）
-BGM：仮BGM_緊迫</t>
+BGM：BGM_緊迫</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
@@ -8040,7 +8040,7 @@
       <c r="E115" s="6" t="n"/>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_不穏</t>
+          <t>BGM：BGM_不穏</t>
         </is>
       </c>
       <c r="G115" s="6" t="n"/>
@@ -8477,7 +8477,7 @@
       <c r="F3" s="7" t="inlineStr">
         <is>
           <t>背景：車内（ハマー）
-BGM：仮BGM_不穏
+BGM：BGM_不穏
 SE：車の走行（ループ・小さめ）</t>
         </is>
       </c>
@@ -8832,7 +8832,7 @@
         <is>
           <t>SE：殴打（ゲンコツ）
 画面揺れ（小）
-BGM：仮BGM_日常コミカル</t>
+BGM：BGM_日常コミカル</t>
         </is>
       </c>
       <c r="G17" s="6" t="n"/>
@@ -9210,7 +9210,7 @@
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_しんみり</t>
+          <t>BGM：BGM_しんみり</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -10119,7 +10119,7 @@
         <is>
           <t>回想終了：暗転明け
 背景：車内（ハマー）
-BGM：仮BGM_しんみり</t>
+BGM：BGM_しんみり</t>
         </is>
       </c>
       <c r="G66" s="6" t="n"/>
@@ -10506,7 +10506,7 @@
           <t>暗転明け
 背景：街中（車体爆発）
 SE：炎が燃える音（ループ）
-BGM：仮BGM_バトル</t>
+BGM：BGM_バトル</t>
         </is>
       </c>
       <c r="G81" s="6" t="n"/>
@@ -10663,7 +10663,7 @@
       <c r="E87" s="6" t="n"/>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_緊迫
+          <t>BGM：BGM_緊迫
 白蛇の男 登場</t>
         </is>
       </c>
@@ -11097,7 +11097,7 @@
       <c r="F104" s="7" t="inlineStr">
         <is>
           <t>SE：走る足音
-BGM：仮BGM_バトル</t>
+BGM：BGM_バトル</t>
         </is>
       </c>
       <c r="G104" s="6" t="n"/>
@@ -11390,7 +11390,7 @@
         <is>
           <t>背景：黒
 SE：走る足音
-BGM：仮BGM_スラム</t>
+BGM：BGM_スラム</t>
         </is>
       </c>
       <c r="G3" s="6" t="n"/>
@@ -12707,7 +12707,7 @@
       <c r="E55" s="6" t="n"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_日常コミカル</t>
+          <t>BGM：BGM_日常コミカル</t>
         </is>
       </c>
       <c r="G55" s="6" t="n"/>
@@ -13274,7 +13274,7 @@
       <c r="E77" s="6" t="n"/>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_日常コミカル
+          <t>BGM：BGM_日常コミカル
 美鈴の表情：怒り</t>
         </is>
       </c>
@@ -13502,7 +13502,7 @@
       <c r="E86" s="6" t="n"/>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_バトル
+          <t>BGM：BGM_バトル
 美鈴の表情：喜び</t>
         </is>
       </c>
@@ -14032,7 +14032,7 @@
       <c r="F3" s="7" t="inlineStr">
         <is>
           <t>背景：黒
-BGM：仮BGM_バトル
+BGM：BGM_バトル
 SE：銃撃戦（連射）※ループ</t>
         </is>
       </c>
@@ -14150,7 +14150,7 @@
       <c r="F8" s="7" t="inlineStr">
         <is>
           <t>背景：会社のエントランス（戦闘後）
-BGM：仮BGM_緊迫
+BGM：BGM_緊迫
 美鈴の表情：喜び</t>
         </is>
       </c>
@@ -15317,7 +15317,7 @@
       <c r="E54" s="6" t="n"/>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_不穏</t>
+          <t>BGM：BGM_不穏</t>
         </is>
       </c>
       <c r="G54" s="6" t="n"/>
@@ -15798,7 +15798,7 @@
       <c r="E74" s="6" t="n"/>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_決意</t>
+          <t>BGM：BGM_決意</t>
         </is>
       </c>
       <c r="G74" s="6" t="n"/>
@@ -16394,7 +16394,7 @@
       <c r="F3" s="7" t="inlineStr">
         <is>
           <t>背景：プライベートジェットの機内
-BGM：仮BGM_しんみり
+BGM：BGM_しんみり
 SE：機内環境音（ループ）</t>
         </is>
       </c>
@@ -16451,7 +16451,7 @@
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_日常コミカル
+          <t>BGM：BGM_日常コミカル
 美鈴の表情：喜び</t>
         </is>
       </c>
@@ -17166,7 +17166,7 @@
       <c r="E34" s="6" t="n"/>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_決意</t>
+          <t>BGM：BGM_決意</t>
         </is>
       </c>
       <c r="G34" s="6" t="n"/>
@@ -17372,7 +17372,7 @@
       <c r="E42" s="6" t="n"/>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_しんみり
+          <t>BGM：BGM_しんみり
 美鈴の表情：通常</t>
         </is>
       </c>
@@ -17809,7 +17809,7 @@
         <is>
           <t>SE：殴打（ゲンコツ）
 画面揺れ（小）
-BGM：仮BGM_日常コミカル</t>
+BGM：BGM_日常コミカル</t>
         </is>
       </c>
       <c r="G59" s="6" t="n"/>
@@ -18109,7 +18109,7 @@
       <c r="E71" s="6" t="n"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_しんみり</t>
+          <t>BGM：BGM_しんみり</t>
         </is>
       </c>
       <c r="G71" s="6" t="n"/>
@@ -18403,7 +18403,7 @@
         <is>
           <t>回想終了：暗転明け
 背景：プライベートジェットの機内
-BGM：仮BGM_しんみり</t>
+BGM：BGM_しんみり</t>
         </is>
       </c>
       <c r="G82" s="6" t="n"/>
@@ -18700,7 +18700,7 @@
       <c r="E93" s="6" t="n"/>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_日常コミカル</t>
+          <t>BGM：BGM_日常コミカル</t>
         </is>
       </c>
       <c r="G93" s="6" t="n"/>
@@ -18933,7 +18933,7 @@
       <c r="E102" s="6" t="n"/>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_決意
+          <t>BGM：BGM_決意
 美鈴の表情：喜び</t>
         </is>
       </c>
@@ -19096,7 +19096,7 @@
       <c r="E108" s="6" t="n"/>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>BGM：仮BGM_しんみり
+          <t>BGM：BGM_しんみり
 美鈴の表情：目閉じ</t>
         </is>
       </c>
@@ -19311,7 +19311,7 @@
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>ファイル名（案）</t>
+          <t>ファイル名</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
@@ -19351,9 +19351,9 @@
           <t>mirei/002_suzuno_normal.png</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -19388,9 +19388,9 @@
           <t>mirei/002_suzuno_happy.png</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -19425,9 +19425,9 @@
           <t>mirei/002_suzuno_angry.png</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -19462,9 +19462,9 @@
           <t>mirei/002_suzuno_sad.png</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -19499,9 +19499,9 @@
           <t>mirei/002_suzuno_tere.png</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -20007,12 +20007,12 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>airplane.jpg</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>airplane.png</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -20044,12 +20044,12 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>airport.jpg</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>airport.png</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -20081,12 +20081,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>car_hummer.jpg</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>car_hummer.png</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -20118,12 +20118,12 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>street.jpg</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>street.png</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -20155,12 +20155,12 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>street_explosion.jpg</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>street_explosion.png</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -20192,12 +20192,12 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>restaurant.jpg</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>restaurant.png</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -20229,12 +20229,12 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>slum.jpg</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>slum.png</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>haioku.jpg</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>haioku.png</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -20299,12 +20299,12 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>armory.jpg</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>armory.png</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -20336,12 +20336,12 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>car_benz.jpg</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>car_benz.png</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -20373,12 +20373,12 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>office_entrance.jpg</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>office_entrance.png</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -20410,12 +20410,12 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>jet.jpg</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>jet.png</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -20474,22 +20474,22 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>曲調で仮指定</t>
+          <t>選曲済み</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>仮BGM_不穏</t>
+          <t>BGM_不穏</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>要調達（選曲）</t>
+          <t>fuon.mp3</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>重く不穏。陰謀や裏切りが明らかになる場面</t>
+          <t>曲名：不穏。重く不穏。陰謀や裏切りが明らかになる場面</t>
         </is>
       </c>
     </row>
@@ -20511,22 +20511,22 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>曲調で仮指定</t>
+          <t>選曲済み</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>仮BGM_日常コミカル</t>
+          <t>BGM_日常コミカル</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>要調達（選曲）</t>
+          <t>nandeshou.mp3</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>軽快でコミカル。美鈴との掛け合い</t>
+          <t>曲名：なんでしょう？。軽快でコミカル。美鈴との掛け合い</t>
         </is>
       </c>
     </row>
@@ -20548,22 +20548,22 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>曲調で仮指定</t>
+          <t>選曲済み</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>仮BGM_緊迫</t>
+          <t>BGM_緊迫</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>要調達（選曲）</t>
+          <t>devil_disaster.mp3</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>張り詰めた緊張感。襲撃の直前、尋問</t>
+          <t>曲名：Devil Disaster。張り詰めた緊張感。襲撃の直前、尋問</t>
         </is>
       </c>
     </row>
@@ -20585,22 +20585,22 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>曲調で仮指定</t>
+          <t>選曲済み</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>仮BGM_バトル</t>
+          <t>BGM_バトル</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>要調達（選曲）</t>
+          <t>kiki.mp3</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -20610,7 +20610,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>激しいアクション。銃撃戦、突入</t>
+          <t>曲名：危機。激しいアクション。銃撃戦、突入</t>
         </is>
       </c>
     </row>
@@ -20622,22 +20622,22 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>曲調で仮指定</t>
+          <t>選曲済み</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>仮BGM_スラム</t>
+          <t>BGM_スラム</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>要調達（選曲）</t>
+          <t>asia_kanrakugai.mp3</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>アジアの裏路地風の、怪しげで猥雑な曲</t>
+          <t>曲名：アジア歓楽街。アジアの裏路地風の、怪しげで猥雑な曲</t>
         </is>
       </c>
     </row>
@@ -20659,22 +20659,22 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>曲調で仮指定</t>
+          <t>選曲済み</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>仮BGM_しんみり</t>
+          <t>BGM_しんみり</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>要調達（選曲）</t>
+          <t>kamikakushinoshinsou.mp3</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -20684,7 +20684,7 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>静かで少し切ない。過去の話、回想のあと、寝顔</t>
+          <t>曲名：神隠しの真相。静かで少し切ない。過去の話、回想のあと、寝顔</t>
         </is>
       </c>
     </row>
@@ -20696,22 +20696,22 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>曲調で仮指定</t>
+          <t>選曲済み</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>仮BGM_決意</t>
+          <t>BGM_決意</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>要調達（選曲）</t>
+          <t>determination.mp3</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -20721,7 +20721,7 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>前向きで力強い。東京へ向かう決意</t>
+          <t>曲名：Determination。前向きで力強い。東京へ向かう決意</t>
         </is>
       </c>
     </row>
@@ -20743,12 +20743,12 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>punch_light.ogg</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>punch_light.mp3</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -20780,12 +20780,12 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>punch_heavy.ogg</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>punch_heavy.mp3</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -20817,12 +20817,12 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>gun_shot.ogg</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>gun_shot.mp3</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -20854,12 +20854,12 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>gun_fight.ogg</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>gun_fight.mp3</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -20891,12 +20891,12 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>gun_cock.ogg</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>gun_cock.mp3</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -20928,12 +20928,12 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>explosion.ogg</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>explosion.mp3</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -20965,12 +20965,12 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>fire.ogg</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>Ambience/fire.mp3</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -21002,12 +21002,12 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>car_door.ogg</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>car_door.mp3</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -21035,12 +21035,12 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>car_drive.ogg</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>Ambience/car_drive.mp3</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -21072,12 +21072,12 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>car_start.ogg</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>car_start.mp3</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -21105,12 +21105,12 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>car_skid.ogg</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>car_skid.mp3</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -21142,12 +21142,12 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>car_crash.ogg</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>car_crash.mp3</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -21179,12 +21179,12 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>glass_break.ogg</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>glass_break.mp3</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -21216,12 +21216,12 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>fall.ogg</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>fall.mp3</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -21249,12 +21249,12 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>door_open.ogg</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>door_open.mp3</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -21286,12 +21286,12 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>airplane_ambience.ogg</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+          <t>Ambience/airplane_ambience.mp3</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">

--- a/docs/【キャラ_002】ときめきポケット_03稿.xlsx
+++ b/docs/【キャラ_002】ときめきポケット_03稿.xlsx
@@ -19538,7 +19538,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>生成AIで作成（用意できなければ通常で代用）</t>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -19573,9 +19573,9 @@
           <t>oji/002_oji_fear.png</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F8" s="6" t="n"/>
@@ -19606,9 +19606,9 @@
           <t>oji/002_oji_rage.png</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F9" s="6" t="n"/>
@@ -19639,9 +19639,9 @@
           <t>oji/002_oji_weak.png</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F10" s="6" t="n"/>
@@ -19672,9 +19672,9 @@
           <t>shisho/002_shisho_normal.png</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F11" s="6" t="n"/>
@@ -19705,9 +19705,9 @@
           <t>shisho/002_shisho_laugh.png</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F12" s="6" t="n"/>
@@ -19738,9 +19738,9 @@
           <t>russian/002_russian_hurt.png</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F13" s="6" t="n"/>
@@ -19771,9 +19771,9 @@
           <t>hakuja/002_hakuja_normal.png</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F14" s="6" t="n"/>
@@ -19804,9 +19804,9 @@
           <t>hakuja/002_hakuja_hurt.png</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F15" s="6" t="n"/>
@@ -19837,9 +19837,9 @@
           <t>tencho/002_tencho_fear.png</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F16" s="6" t="n"/>
@@ -20450,9 +20450,9 @@
           <t>event_002.jpg</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>要調達</t>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>納品済み</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
